--- a/results/07-2025/beta/inputs-07-2025.xlsx
+++ b/results/07-2025/beta/inputs-07-2025.xlsx
@@ -36393,7 +36393,7 @@
         <v>-1</v>
       </c>
       <c r="M223" t="n">
-        <v>1928.06848984305</v>
+        <v>1930.49784263293</v>
       </c>
       <c r="N223" t="n">
         <v>420.041098704141</v>
@@ -36456,10 +36456,10 @@
         <v>0</v>
       </c>
       <c r="AH223" t="n">
-        <v>1843.14908029657</v>
+        <v>1842.80088023162</v>
       </c>
       <c r="AI223" t="n">
-        <v>306.330805548024</v>
+        <v>306.169972587707</v>
       </c>
       <c r="AJ223" t="n">
         <v>-2702.60616739443</v>
@@ -36507,10 +36507,10 @@
         <v>0.28035</v>
       </c>
       <c r="AY223" t="n">
-        <v>1607.75799306673</v>
+        <v>1607.67964805212</v>
       </c>
       <c r="AZ223" t="n">
-        <v>269.479981248305</v>
+        <v>269.443793832234</v>
       </c>
     </row>
     <row r="224">
@@ -36551,7 +36551,7 @@
         <v>-1</v>
       </c>
       <c r="M224" t="n">
-        <v>1933.7193945079</v>
+        <v>1936.14876935853</v>
       </c>
       <c r="N224" t="n">
         <v>422.730332867314</v>
@@ -36569,7 +36569,7 @@
         <v>2598.17826136013</v>
       </c>
       <c r="S224" t="n">
-        <v>554.586742090733</v>
+        <v>154.586742090733</v>
       </c>
       <c r="T224" t="n">
         <v>103.083510693309</v>
@@ -36614,10 +36614,10 @@
         <v>0</v>
       </c>
       <c r="AH224" t="n">
-        <v>1871.06898261094</v>
+        <v>1870.36105052968</v>
       </c>
       <c r="AI224" t="n">
-        <v>310.579313133025</v>
+        <v>310.254107821905</v>
       </c>
       <c r="AJ224" t="n">
         <v>-2737.12914333107</v>
@@ -36626,7 +36626,7 @@
         <v>-1505.98764777114</v>
       </c>
       <c r="AL224" t="n">
-        <v>-191.903281866846</v>
+        <v>-178.569948533512</v>
       </c>
       <c r="AM224" t="n">
         <v>-66.557883965999</v>
@@ -36665,10 +36665,10 @@
         <v>0.250425</v>
       </c>
       <c r="AY224" t="n">
-        <v>1639.17518915419</v>
+        <v>1638.93755942129</v>
       </c>
       <c r="AZ224" t="n">
-        <v>273.848651703236</v>
+        <v>273.739293092163</v>
       </c>
     </row>
     <row r="225">
@@ -36709,7 +36709,7 @@
         <v>-1</v>
       </c>
       <c r="M225" t="n">
-        <v>1953.9458491201</v>
+        <v>1964.80704060979</v>
       </c>
       <c r="N225" t="n">
         <v>421.560366230639</v>
@@ -36727,7 +36727,7 @@
         <v>2624.88199724452</v>
       </c>
       <c r="S225" t="n">
-        <v>551.160020209622</v>
+        <v>153.63157001133</v>
       </c>
       <c r="T225" t="n">
         <v>109.658761987664</v>
@@ -36736,7 +36736,7 @@
         <v>172.355545528645</v>
       </c>
       <c r="V225" t="n">
-        <v>2264.16875</v>
+        <v>2258.198</v>
       </c>
       <c r="W225" t="n">
         <v>238.176195410118</v>
@@ -36772,10 +36772,10 @@
         <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1895.09140261663</v>
+        <v>1897.86433298005</v>
       </c>
       <c r="AI225" t="n">
-        <v>314.309323883574</v>
+        <v>315.586832106953</v>
       </c>
       <c r="AJ225" t="n">
         <v>-2768.14017675223</v>
@@ -36784,13 +36784,13 @@
         <v>-1523.95735923652</v>
       </c>
       <c r="AL225" t="n">
-        <v>-196.711949207166</v>
+        <v>-170.12766753389</v>
       </c>
       <c r="AM225" t="n">
         <v>-66.8964021502872</v>
       </c>
       <c r="AN225" t="n">
-        <v>2041.01161875</v>
+        <v>2039.6682</v>
       </c>
       <c r="AO225" t="n">
         <v>207.648735205414</v>
@@ -36823,10 +36823,10 @@
         <v>0.222075</v>
       </c>
       <c r="AY225" t="n">
-        <v>1666.49387974293</v>
+        <v>1666.8801593418</v>
       </c>
       <c r="AZ225" t="n">
-        <v>279.40262457704</v>
+        <v>279.580705316227</v>
       </c>
     </row>
     <row r="226">
@@ -36867,7 +36867,7 @@
         <v>-1</v>
       </c>
       <c r="M226" t="n">
-        <v>1964.03675030733</v>
+        <v>2000.12533264478</v>
       </c>
       <c r="N226" t="n">
         <v>424.4289988</v>
@@ -36879,13 +36879,13 @@
         <v>3340.03573828971</v>
       </c>
       <c r="Q226" t="n">
-        <v>4626.76194039491</v>
+        <v>4730.74660445738</v>
       </c>
       <c r="R226" t="n">
         <v>2649.44053129257</v>
       </c>
       <c r="S226" t="n">
-        <v>547.754471612975</v>
+        <v>410.982299820336</v>
       </c>
       <c r="T226" t="n">
         <v>134.709036355557</v>
@@ -36894,7 +36894,7 @@
         <v>172.564054494644</v>
       </c>
       <c r="V226" t="n">
-        <v>2307.435690501</v>
+        <v>2303.455190501</v>
       </c>
       <c r="W226" t="n">
         <v>241.657946376297</v>
@@ -36930,25 +36930,25 @@
         <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1917.83834514866</v>
+        <v>1924.18988245426</v>
       </c>
       <c r="AI226" t="n">
-        <v>319.681153482203</v>
+        <v>322.637444164292</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2775.5041216313</v>
+        <v>-2787.9822813188</v>
       </c>
       <c r="AK226" t="n">
         <v>-1542.28152731002</v>
       </c>
       <c r="AL226" t="n">
-        <v>-200.493764927599</v>
+        <v>-169.350410861235</v>
       </c>
       <c r="AM226" t="n">
         <v>-67.3585373001086</v>
       </c>
       <c r="AN226" t="n">
-        <v>2051.16759911273</v>
+        <v>2048.92856786273</v>
       </c>
       <c r="AO226" t="n">
         <v>212.83677314008</v>
@@ -36981,10 +36981,10 @@
         <v>0.1953</v>
       </c>
       <c r="AY226" t="n">
-        <v>1693.60825740138</v>
+        <v>1695.42363289401</v>
       </c>
       <c r="AZ226" t="n">
-        <v>281.452634110536</v>
+        <v>282.295880253193</v>
       </c>
     </row>
     <row r="227">
@@ -37025,7 +37025,7 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>1974.53128754204</v>
+        <v>2015.66538114018</v>
       </c>
       <c r="N227" t="n">
         <v>424.522897172307</v>
@@ -37037,13 +37037,13 @@
         <v>3369.56031809787</v>
       </c>
       <c r="Q227" t="n">
-        <v>4658.69179091015</v>
+        <v>4763.19252374503</v>
       </c>
       <c r="R227" t="n">
         <v>2674.98941294424</v>
       </c>
       <c r="S227" t="n">
-        <v>544.369965473725</v>
+        <v>408.442891766269</v>
       </c>
       <c r="T227" t="n">
         <v>155.206844624839</v>
@@ -37052,7 +37052,7 @@
         <v>172.904788658593</v>
       </c>
       <c r="V227" t="n">
-        <v>2311.417440501</v>
+        <v>2309.427190501</v>
       </c>
       <c r="W227" t="n">
         <v>245.190594913367</v>
@@ -37088,25 +37088,25 @@
         <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>1939.4640739092</v>
+        <v>1955.44249641565</v>
       </c>
       <c r="AI227" t="n">
-        <v>326.545530643842</v>
+        <v>325.264298549568</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2784.08407798133</v>
+        <v>-2809.10232560901</v>
       </c>
       <c r="AK227" t="n">
         <v>-1559.44733702866</v>
       </c>
       <c r="AL227" t="n">
-        <v>-204.326097110056</v>
+        <v>-168.651840586777</v>
       </c>
       <c r="AM227" t="n">
         <v>-67.7086969220617</v>
       </c>
       <c r="AN227" t="n">
-        <v>2060.71197322545</v>
+        <v>2058.02513572545</v>
       </c>
       <c r="AO227" t="n">
         <v>215.94810271373</v>
@@ -37139,10 +37139,10 @@
         <v>0.171675</v>
       </c>
       <c r="AY227" t="n">
-        <v>1715.27913096422</v>
+        <v>1720.76799653542</v>
       </c>
       <c r="AZ227" t="n">
-        <v>286.000947257095</v>
+        <v>286.592103594612</v>
       </c>
     </row>
     <row r="228">
@@ -37183,7 +37183,7 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>1985.83309687173</v>
+        <v>2033.02179894024</v>
       </c>
       <c r="N228" t="n">
         <v>428.448339862007</v>
@@ -37195,13 +37195,13 @@
         <v>3399.64120333114</v>
       </c>
       <c r="Q228" t="n">
-        <v>4690.99494810492</v>
+        <v>4796.01431092621</v>
       </c>
       <c r="R228" t="n">
         <v>2698.31224140776</v>
       </c>
       <c r="S228" t="n">
-        <v>541.006371773168</v>
+        <v>405.919174395884</v>
       </c>
       <c r="T228" t="n">
         <v>162.820344255939</v>
@@ -37246,25 +37246,25 @@
         <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1965.0641619591</v>
+        <v>1984.88340620506</v>
       </c>
       <c r="AI228" t="n">
-        <v>329.811944535982</v>
+        <v>330.213754227397</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-2802.00775533023</v>
+        <v>-2833.38924665272</v>
       </c>
       <c r="AK228" t="n">
         <v>-1575.62837412004</v>
       </c>
       <c r="AL228" t="n">
-        <v>-207.296309502495</v>
+        <v>-167.119146399973</v>
       </c>
       <c r="AM228" t="n">
         <v>-67.9364262148734</v>
       </c>
       <c r="AN228" t="n">
-        <v>2070.03354108818</v>
+        <v>2067.34670358817</v>
       </c>
       <c r="AO228" t="n">
         <v>219.104914896297</v>
@@ -37297,10 +37297,10 @@
         <v>0.14805</v>
       </c>
       <c r="AY228" t="n">
-        <v>1736.42804631756</v>
+        <v>1746.53552656238</v>
       </c>
       <c r="AZ228" t="n">
-        <v>290.32828932276</v>
+        <v>291.083024035847</v>
       </c>
     </row>
     <row r="229">
@@ -37341,7 +37341,7 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>2002.79741540264</v>
+        <v>2043.3145583333</v>
       </c>
       <c r="N229" t="n">
         <v>430.402608127864</v>
@@ -37353,13 +37353,13 @@
         <v>3428.99713798472</v>
       </c>
       <c r="Q229" t="n">
-        <v>4723.673788019</v>
+        <v>4829.21435475184</v>
       </c>
       <c r="R229" t="n">
         <v>2723.57333674919</v>
       </c>
       <c r="S229" t="n">
-        <v>537.663561295971</v>
+        <v>403.411050758414</v>
       </c>
       <c r="T229" t="n">
         <v>160.445027356869</v>
@@ -37368,7 +37368,7 @@
         <v>172.940387750349</v>
       </c>
       <c r="V229" t="n">
-        <v>2320.798190501</v>
+        <v>2316.672190501</v>
       </c>
       <c r="W229" t="n">
         <v>252.41157173769</v>
@@ -37404,25 +37404,25 @@
         <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>1988.31850544915</v>
+        <v>2002.08812793393</v>
       </c>
       <c r="AI229" t="n">
-        <v>331.758393127332</v>
+        <v>329.321583987845</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-2817.3531024379</v>
+        <v>-2855.12941779824</v>
       </c>
       <c r="AK229" t="n">
         <v>-1590.76980975328</v>
       </c>
       <c r="AL229" t="n">
-        <v>-209.725094879028</v>
+        <v>-165.07284809192</v>
       </c>
       <c r="AM229" t="n">
         <v>-68.1377724732184</v>
       </c>
       <c r="AN229" t="n">
-        <v>2082.7751652009</v>
+        <v>2080.5033964509</v>
       </c>
       <c r="AO229" t="n">
         <v>222.307874570001</v>
@@ -37455,10 +37455,10 @@
         <v>0.124425</v>
       </c>
       <c r="AY229" t="n">
-        <v>1757.40414445487</v>
+        <v>1769.985880427</v>
       </c>
       <c r="AZ229" t="n">
-        <v>294.254329902606</v>
+        <v>294.173343209048</v>
       </c>
     </row>
     <row r="230">
@@ -37499,7 +37499,7 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>2012.48468054237</v>
+        <v>2053.00186129147</v>
       </c>
       <c r="N230" t="n">
         <v>433.385986</v>
@@ -37511,13 +37511,13 @@
         <v>3457.71231495272</v>
       </c>
       <c r="Q230" t="n">
-        <v>4880.17659654289</v>
+        <v>4959.97196525287</v>
       </c>
       <c r="R230" t="n">
         <v>2750.26808656332</v>
       </c>
       <c r="S230" t="n">
-        <v>534.341405625204</v>
+        <v>412.618424502142</v>
       </c>
       <c r="T230" t="n">
         <v>146.435353395161</v>
@@ -37526,7 +37526,7 @@
         <v>172.609824755473</v>
       </c>
       <c r="V230" t="n">
-        <v>2365.34105938352</v>
+        <v>2365.24405938352</v>
       </c>
       <c r="W230" t="n">
         <v>256.101420894358</v>
@@ -37562,25 +37562,25 @@
         <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>2011.88604277742</v>
+        <v>2032.18374581113</v>
       </c>
       <c r="AI230" t="n">
-        <v>333.716329059215</v>
+        <v>334.235231621928</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-2843.07259713675</v>
+        <v>-2884.12319497301</v>
       </c>
       <c r="AK230" t="n">
         <v>-1605.87324565642</v>
       </c>
       <c r="AL230" t="n">
-        <v>-212.206475066535</v>
+        <v>-163.496795575325</v>
       </c>
       <c r="AM230" t="n">
         <v>-68.2114332984008</v>
       </c>
       <c r="AN230" t="n">
-        <v>2095.80387319947</v>
+        <v>2094.40589194947</v>
       </c>
       <c r="AO230" t="n">
         <v>225.557656336565</v>
@@ -37613,10 +37613,10 @@
         <v>0.1008</v>
       </c>
       <c r="AY230" t="n">
-        <v>1778.56487642134</v>
+        <v>1794.2844996823</v>
       </c>
       <c r="AZ230" t="n">
-        <v>297.412244407434</v>
+        <v>296.782845387016</v>
       </c>
     </row>
     <row r="231">
@@ -37726,19 +37726,19 @@
         <v>0</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-2277.06308615839</v>
+        <v>-2311.78124999068</v>
       </c>
       <c r="AK231" t="n">
         <v>-1288.1947172475</v>
       </c>
       <c r="AL231" t="n">
-        <v>-195.759808399868</v>
+        <v>-147.050128908658</v>
       </c>
       <c r="AM231" t="n">
         <v>-62.7447666317341</v>
       </c>
       <c r="AN231" t="n">
-        <v>1575.73494908674</v>
+        <v>1574.78477408674</v>
       </c>
       <c r="AO231" t="n">
         <v>170.389772481057</v>
@@ -37771,10 +37771,10 @@
         <v>0.0819</v>
       </c>
       <c r="AY231" t="n">
-        <v>1342.18545979177</v>
+        <v>1354.30993798878</v>
       </c>
       <c r="AZ231" t="n">
-        <v>223.939500012569</v>
+        <v>223.598378213363</v>
       </c>
     </row>
     <row r="232">
@@ -37884,19 +37884,19 @@
         <v>0</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-1700.2490023975</v>
+        <v>-1730.17944410719</v>
       </c>
       <c r="AK232" t="n">
         <v>-967.287936372096</v>
       </c>
       <c r="AL232" t="n">
-        <v>-179.323141733201</v>
+        <v>-130.613462241992</v>
       </c>
       <c r="AM232" t="n">
         <v>-57.3247666317341</v>
       </c>
       <c r="AN232" t="n">
-        <v>1054.38133122402</v>
+        <v>1053.43115622402</v>
       </c>
       <c r="AO232" t="n">
         <v>114.415423342211</v>
@@ -37929,10 +37929,10 @@
         <v>0.063</v>
       </c>
       <c r="AY232" t="n">
-        <v>900.046023350978</v>
+        <v>907.711171592638</v>
       </c>
       <c r="AZ232" t="n">
-        <v>149.731812491973</v>
+        <v>149.300283512199</v>
       </c>
     </row>
     <row r="233">
@@ -38042,19 +38042,19 @@
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-1414.81794383831</v>
+        <v>-1444.748385548</v>
       </c>
       <c r="AK233" t="n">
         <v>-809.795016537425</v>
       </c>
       <c r="AL233" t="n">
-        <v>-162.253141733201</v>
+        <v>-113.543462241992</v>
       </c>
       <c r="AM233" t="n">
         <v>-51.8514332984008</v>
       </c>
       <c r="AN233" t="n">
-        <v>532.201738361293</v>
+        <v>532.179913361293</v>
       </c>
       <c r="AO233" t="n">
         <v>57.6228197012306</v>
@@ -38087,10 +38087,10 @@
         <v>0.0441</v>
       </c>
       <c r="AY233" t="n">
-        <v>452.67435962492</v>
+        <v>457.241342807504</v>
       </c>
       <c r="AZ233" t="n">
-        <v>75.0861740383235</v>
+        <v>75.2029271149338</v>
       </c>
     </row>
     <row r="234">
@@ -38200,13 +38200,13 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-1137.21222741462</v>
+        <v>-1160.90358928056</v>
       </c>
       <c r="AK234" t="n">
         <v>-650.82858465987</v>
       </c>
       <c r="AL234" t="n">
-        <v>-144.926475066535</v>
+        <v>-96.216795575325</v>
       </c>
       <c r="AM234" t="n">
         <v>-46.0280999650675</v>
@@ -38358,13 +38358,13 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-857.690719960009</v>
+        <v>-875.112037855855</v>
       </c>
       <c r="AK235" t="n">
         <v>-490.329219883216</v>
       </c>
       <c r="AL235" t="n">
-        <v>-127.029417936046</v>
+        <v>-78.3197384448368</v>
       </c>
       <c r="AM235" t="n">
         <v>-40.2849493479273</v>
@@ -38516,13 +38516,13 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-576.231023073714</v>
+        <v>-587.351179200283</v>
       </c>
       <c r="AK236" t="n">
         <v>-328.43048539875</v>
       </c>
       <c r="AL236" t="n">
-        <v>-108.543193199689</v>
+        <v>-73.1668470418124</v>
       </c>
       <c r="AM236" t="n">
         <v>-34.5368826657351</v>
@@ -38674,13 +38674,13 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-292.810595792573</v>
+        <v>-297.598317915172</v>
       </c>
       <c r="AK237" t="n">
         <v>-165.016085193799</v>
       </c>
       <c r="AL237" t="n">
-        <v>-90.1711925260347</v>
+        <v>-68.0457947081014</v>
       </c>
       <c r="AM237" t="n">
         <v>-28.7916978147803</v>
@@ -38838,7 +38838,7 @@
         <v>0</v>
       </c>
       <c r="AL238" t="n">
-        <v>-71.9127101389355</v>
+        <v>-54.3463847140902</v>
       </c>
       <c r="AM238" t="n">
         <v>-23.0395626649588</v>
@@ -38996,7 +38996,7 @@
         <v>0</v>
       </c>
       <c r="AL239" t="n">
-        <v>-53.7670446231447</v>
+        <v>-40.7316216552146</v>
       </c>
       <c r="AM239" t="n">
         <v>-17.2760697096724</v>
@@ -39154,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="AL240" t="n">
-        <v>-35.7334988973724</v>
+        <v>-27.2009825086852</v>
       </c>
       <c r="AM240" t="n">
         <v>-11.5183404168607</v>
@@ -39312,7 +39312,7 @@
         <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>-17.8113801875068</v>
+        <v>-13.7539474834047</v>
       </c>
       <c r="AM241" t="n">
         <v>-5.75366082518242</v>

--- a/results/07-2025/beta/inputs-07-2025.xlsx
+++ b/results/07-2025/beta/inputs-07-2025.xlsx
@@ -839,10 +839,10 @@
     <t xml:space="preserve">2025 Q2</t>
   </si>
   <si>
-    <t xml:space="preserve">projection</t>
+    <t xml:space="preserve">2025 Q3</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 Q3</t>
+    <t xml:space="preserve">projection</t>
   </si>
   <si>
     <t xml:space="preserve">2025 Q4</t>
@@ -36360,70 +36360,70 @@
         <v>274</v>
       </c>
       <c r="B223" t="s">
-        <v>275</v>
+        <v>53</v>
       </c>
       <c r="C223" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D223" t="n">
-        <v>0.00380322207945549</v>
+        <v>0.0149204426581513</v>
       </c>
       <c r="E223" t="n">
-        <v>0.00707611529348728</v>
+        <v>0.00175881733093664</v>
       </c>
       <c r="F223" t="n">
-        <v>0.00707611529348728</v>
+        <v>0.00126785439461785</v>
       </c>
       <c r="G223" t="n">
-        <v>0.00707611529348728</v>
+        <v>0.00165780203080734</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00421913212212344</v>
+        <v>0.00515919459239966</v>
       </c>
       <c r="I223" t="n">
         <v>0.00571780133544419</v>
       </c>
       <c r="J223" t="n">
-        <v>30270.6630581958</v>
+        <v>30331.1</v>
       </c>
       <c r="K223" t="n">
-        <v>20701.385550235</v>
+        <v>20640.9</v>
       </c>
       <c r="L223" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="M223" t="n">
-        <v>1930.49784263293</v>
+        <v>1938.7</v>
       </c>
       <c r="N223" t="n">
-        <v>420.041098704141</v>
+        <v>400.7276195</v>
       </c>
       <c r="O223" t="n">
         <v>75.203</v>
       </c>
       <c r="P223" t="n">
-        <v>3247.89614191079</v>
+        <v>3251</v>
       </c>
       <c r="Q223" t="n">
-        <v>4709.81806162029</v>
+        <v>4871.2</v>
       </c>
       <c r="R223" t="n">
-        <v>2571.06880339937</v>
+        <v>2584.7</v>
       </c>
       <c r="S223" t="n">
-        <v>536.911713914646</v>
+        <v>0</v>
       </c>
       <c r="T223" t="n">
         <v>88.3944428040623</v>
       </c>
       <c r="U223" t="n">
-        <v>172.294518514206</v>
+        <v>0</v>
       </c>
       <c r="V223" t="n">
-        <v>2268.998</v>
+        <v>2352.098</v>
       </c>
       <c r="W223" t="n">
-        <v>231.362463474923</v>
+        <v>218.9</v>
       </c>
       <c r="X223" t="n">
         <v>0</v>
@@ -36435,10 +36435,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="AB223" t="n">
-        <v>96.979</v>
+        <v>116.5</v>
       </c>
       <c r="AC223" t="n">
         <v>-0.901</v>
@@ -36453,31 +36453,31 @@
         <v>2.6696</v>
       </c>
       <c r="AG223" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AH223" t="n">
-        <v>1842.80088023162</v>
+        <v>1862.758</v>
       </c>
       <c r="AI223" t="n">
-        <v>306.169972587707</v>
+        <v>302.442</v>
       </c>
       <c r="AJ223" t="n">
-        <v>-2702.60616739443</v>
+        <v>-2721.972</v>
       </c>
       <c r="AK223" t="n">
-        <v>-1488.27825640792</v>
+        <v>-1489.914</v>
       </c>
       <c r="AL223" t="n">
-        <v>-186.823723797155</v>
+        <v>-168.926666666667</v>
       </c>
       <c r="AM223" t="n">
-        <v>-66.1131506171401</v>
+        <v>-60.3699999999999</v>
       </c>
       <c r="AN223" t="n">
-        <v>1992.035925</v>
+        <v>2010.733425</v>
       </c>
       <c r="AO223" t="n">
-        <v>200.084054281858</v>
+        <v>197.28</v>
       </c>
       <c r="AP223" t="n">
         <v>0</v>
@@ -36489,10 +36489,10 @@
         <v>0</v>
       </c>
       <c r="AS223" t="n">
-        <v>32.396</v>
+        <v>32.596</v>
       </c>
       <c r="AT223" t="n">
-        <v>53.8556355</v>
+        <v>54.821925</v>
       </c>
       <c r="AU223" t="n">
         <v>2.745007</v>
@@ -36504,27 +36504,27 @@
         <v>2.35332026</v>
       </c>
       <c r="AX223" t="n">
-        <v>0.28035</v>
+        <v>0.315</v>
       </c>
       <c r="AY223" t="n">
-        <v>1607.67964805212</v>
+        <v>1612.17</v>
       </c>
       <c r="AZ223" t="n">
-        <v>269.443793832234</v>
+        <v>268.605</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
+        <v>275</v>
+      </c>
+      <c r="B224" t="s">
         <v>276</v>
       </c>
-      <c r="B224" t="s">
-        <v>275</v>
-      </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.00366224990092978</v>
+        <v>0.00612589701812283</v>
       </c>
       <c r="E224" t="n">
         <v>0.00774551207611962</v>
@@ -36542,34 +36542,34 @@
         <v>0.00573662843673683</v>
       </c>
       <c r="J224" t="n">
-        <v>30572.6312556278</v>
+        <v>30633.6710925302</v>
       </c>
       <c r="K224" t="n">
-        <v>20906.5721816783</v>
+        <v>20845.4871147455</v>
       </c>
       <c r="L224" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="M224" t="n">
-        <v>1936.14876935853</v>
+        <v>1963.86342701628</v>
       </c>
       <c r="N224" t="n">
-        <v>422.730332867314</v>
+        <v>403.2265501007</v>
       </c>
       <c r="O224" t="n">
         <v>75.203</v>
       </c>
       <c r="P224" t="n">
-        <v>3277.57851612576</v>
+        <v>3280.71074023201</v>
       </c>
       <c r="Q224" t="n">
-        <v>4733.39146613866</v>
+        <v>4884.27813591109</v>
       </c>
       <c r="R224" t="n">
-        <v>2598.17826136013</v>
+        <v>2610.41793496548</v>
       </c>
       <c r="S224" t="n">
-        <v>154.586742090733</v>
+        <v>140.192005864581</v>
       </c>
       <c r="T224" t="n">
         <v>103.083510693309</v>
@@ -36578,7 +36578,7 @@
         <v>172.442000465766</v>
       </c>
       <c r="V224" t="n">
-        <v>2275.698</v>
+        <v>2359.387155</v>
       </c>
       <c r="W224" t="n">
         <v>234.744608694576</v>
@@ -36596,7 +36596,7 @@
         <v>35.7</v>
       </c>
       <c r="AB224" t="n">
-        <v>96.979</v>
+        <v>117.401</v>
       </c>
       <c r="AC224" t="n">
         <v>-0.901</v>
@@ -36608,34 +36608,34 @@
         <v>2.372</v>
       </c>
       <c r="AF224" t="n">
-        <v>2.693006</v>
+        <v>-8.306994</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
       </c>
       <c r="AH224" t="n">
-        <v>1870.36105052968</v>
+        <v>1884.43061146495</v>
       </c>
       <c r="AI224" t="n">
-        <v>310.254107821905</v>
+        <v>312.682511280734</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-2737.12914333107</v>
+        <v>-2774.60137630933</v>
       </c>
       <c r="AK224" t="n">
-        <v>-1505.98764777114</v>
+        <v>-1509.09215219586</v>
       </c>
       <c r="AL224" t="n">
-        <v>-178.569948533512</v>
+        <v>-160.193066862153</v>
       </c>
       <c r="AM224" t="n">
-        <v>-66.557883965999</v>
+        <v>-60.8147333488588</v>
       </c>
       <c r="AN224" t="n">
-        <v>2019.8232</v>
+        <v>2057.350759875</v>
       </c>
       <c r="AO224" t="n">
-        <v>203.041591238137</v>
+        <v>200.23753695628</v>
       </c>
       <c r="AP224" t="n">
         <v>0</v>
@@ -36647,10 +36647,10 @@
         <v>0</v>
       </c>
       <c r="AS224" t="n">
-        <v>32.467</v>
+        <v>32.637</v>
       </c>
       <c r="AT224" t="n">
-        <v>48.24863775</v>
+        <v>50.0940495</v>
       </c>
       <c r="AU224" t="n">
         <v>0.855474</v>
@@ -36659,16 +36659,16 @@
         <v>2.58402</v>
       </c>
       <c r="AW224" t="n">
-        <v>2.39286449</v>
+        <v>0.19286449</v>
       </c>
       <c r="AX224" t="n">
-        <v>0.250425</v>
+        <v>0.28035</v>
       </c>
       <c r="AY224" t="n">
-        <v>1638.93755942129</v>
+        <v>1646.59356257961</v>
       </c>
       <c r="AZ224" t="n">
-        <v>273.739293092163</v>
+        <v>273.446890038165</v>
       </c>
     </row>
     <row r="225">
@@ -36676,13 +36676,13 @@
         <v>277</v>
       </c>
       <c r="B225" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.00375865650532581</v>
+        <v>0.00597611620667493</v>
       </c>
       <c r="E225" t="n">
         <v>0.00800202664149885</v>
@@ -36694,40 +36694,40 @@
         <v>0.00800202664149885</v>
       </c>
       <c r="H225" t="n">
-        <v>0.00545800076174396</v>
+        <v>0.0059495417545925</v>
       </c>
       <c r="I225" t="n">
         <v>0.00571666765914358</v>
       </c>
       <c r="J225" t="n">
-        <v>30865.6063565116</v>
+        <v>30927.2311333305</v>
       </c>
       <c r="K225" t="n">
-        <v>21104.6384559209</v>
+        <v>21042.9746766333</v>
       </c>
       <c r="L225" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="M225" t="n">
-        <v>1964.80704060979</v>
+        <v>1975.63341707228</v>
       </c>
       <c r="N225" t="n">
-        <v>421.560366230639</v>
+        <v>401.864404763182</v>
       </c>
       <c r="O225" t="n">
         <v>75.203</v>
       </c>
       <c r="P225" t="n">
-        <v>3308.36903905948</v>
+        <v>3311.53068818719</v>
       </c>
       <c r="Q225" t="n">
-        <v>4757.1843093198</v>
+        <v>4968.92969341018</v>
       </c>
       <c r="R225" t="n">
-        <v>2624.88199724452</v>
+        <v>2637.25905250979</v>
       </c>
       <c r="S225" t="n">
-        <v>153.63157001133</v>
+        <v>394.325777053842</v>
       </c>
       <c r="T225" t="n">
         <v>109.658761987664</v>
@@ -36736,7 +36736,7 @@
         <v>172.355545528645</v>
       </c>
       <c r="V225" t="n">
-        <v>2258.198</v>
+        <v>2351.492755775</v>
       </c>
       <c r="W225" t="n">
         <v>238.176195410118</v>
@@ -36754,7 +36754,7 @@
         <v>35.7</v>
       </c>
       <c r="AB225" t="n">
-        <v>101.318</v>
+        <v>121.74</v>
       </c>
       <c r="AC225" t="n">
         <v>-2.15</v>
@@ -36766,34 +36766,34 @@
         <v>0.49</v>
       </c>
       <c r="AF225" t="n">
-        <v>2.71754</v>
+        <v>-8.28246</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1897.86433298005</v>
+        <v>1912.00537081367</v>
       </c>
       <c r="AI225" t="n">
-        <v>315.586832106953</v>
+        <v>317.233052316878</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-2768.14017675223</v>
+        <v>-2821.33893951855</v>
       </c>
       <c r="AK225" t="n">
-        <v>-1523.95735923652</v>
+        <v>-1527.72923849703</v>
       </c>
       <c r="AL225" t="n">
-        <v>-170.12766753389</v>
+        <v>-159.773926097281</v>
       </c>
       <c r="AM225" t="n">
-        <v>-66.8964021502872</v>
+        <v>-61.153251533147</v>
       </c>
       <c r="AN225" t="n">
-        <v>2039.6682</v>
+        <v>2098.18707992438</v>
       </c>
       <c r="AO225" t="n">
-        <v>207.648735205414</v>
+        <v>204.844680923556</v>
       </c>
       <c r="AP225" t="n">
         <v>0</v>
@@ -36805,10 +36805,10 @@
         <v>0</v>
       </c>
       <c r="AS225" t="n">
-        <v>32.466</v>
+        <v>32.626</v>
       </c>
       <c r="AT225" t="n">
-        <v>45.35351775</v>
+        <v>48.02804775</v>
       </c>
       <c r="AU225" t="n">
         <v>0.573855</v>
@@ -36817,16 +36817,16 @@
         <v>2.04112</v>
       </c>
       <c r="AW225" t="n">
-        <v>2.42854317</v>
+        <v>-1.64145683</v>
       </c>
       <c r="AX225" t="n">
-        <v>0.222075</v>
+        <v>0.250425</v>
       </c>
       <c r="AY225" t="n">
-        <v>1666.8801593418</v>
+        <v>1677.71789601269</v>
       </c>
       <c r="AZ225" t="n">
-        <v>279.580705316227</v>
+        <v>279.658701809463</v>
       </c>
     </row>
     <row r="226">
@@ -36834,7 +36834,7 @@
         <v>278</v>
       </c>
       <c r="B226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -36858,34 +36858,34 @@
         <v>0.00567994383495618</v>
       </c>
       <c r="J226" t="n">
-        <v>31168.2740170085</v>
+        <v>31230.5030854396</v>
       </c>
       <c r="K226" t="n">
-        <v>21285.254840686</v>
+        <v>21223.0633343345</v>
       </c>
       <c r="L226" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="M226" t="n">
-        <v>2000.12533264478</v>
+        <v>2011.14631810331</v>
       </c>
       <c r="N226" t="n">
-        <v>424.4289988</v>
+        <v>404.538965016832</v>
       </c>
       <c r="O226" t="n">
         <v>75.203</v>
       </c>
       <c r="P226" t="n">
-        <v>3340.03573828971</v>
+        <v>3343.22764975842</v>
       </c>
       <c r="Q226" t="n">
-        <v>4730.74660445738</v>
+        <v>4977.93145125724</v>
       </c>
       <c r="R226" t="n">
-        <v>2649.44053129257</v>
+        <v>2661.94500876973</v>
       </c>
       <c r="S226" t="n">
-        <v>410.982299820336</v>
+        <v>391.889287563627</v>
       </c>
       <c r="T226" t="n">
         <v>134.709036355557</v>
@@ -36894,7 +36894,7 @@
         <v>172.564054494644</v>
       </c>
       <c r="V226" t="n">
-        <v>2303.455190501</v>
+        <v>2405.12553055388</v>
       </c>
       <c r="W226" t="n">
         <v>241.657946376297</v>
@@ -36912,7 +36912,7 @@
         <v>35.7</v>
       </c>
       <c r="AB226" t="n">
-        <v>99.168</v>
+        <v>119.59</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -36924,34 +36924,34 @@
         <v>0</v>
       </c>
       <c r="AF226" t="n">
-        <v>2.71754</v>
+        <v>-8.28246</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1924.18988245426</v>
+        <v>1938.51561009222</v>
       </c>
       <c r="AI226" t="n">
-        <v>322.637444164292</v>
+        <v>323.36378624361</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2787.9822813188</v>
+        <v>-2861.79002551476</v>
       </c>
       <c r="AK226" t="n">
-        <v>-1542.28152731002</v>
+        <v>-1546.81956345147</v>
       </c>
       <c r="AL226" t="n">
-        <v>-169.350410861235</v>
+        <v>-158.360235682735</v>
       </c>
       <c r="AM226" t="n">
-        <v>-67.3585373001086</v>
+        <v>-61.6153866829684</v>
       </c>
       <c r="AN226" t="n">
-        <v>2048.92856786273</v>
+        <v>2130.323274299</v>
       </c>
       <c r="AO226" t="n">
-        <v>212.83677314008</v>
+        <v>210.032718858223</v>
       </c>
       <c r="AP226" t="n">
         <v>0</v>
@@ -36963,10 +36963,10 @@
         <v>0</v>
       </c>
       <c r="AS226" t="n">
-        <v>32.484</v>
+        <v>32.634</v>
       </c>
       <c r="AT226" t="n">
-        <v>44.79930675</v>
+        <v>48.2570055</v>
       </c>
       <c r="AU226" t="n">
         <v>0.378236</v>
@@ -36975,16 +36975,16 @@
         <v>1.53068</v>
       </c>
       <c r="AW226" t="n">
-        <v>2.44287734</v>
+        <v>-3.38712266</v>
       </c>
       <c r="AX226" t="n">
-        <v>0.1953</v>
+        <v>0.222075</v>
       </c>
       <c r="AY226" t="n">
-        <v>1695.42363289401</v>
+        <v>1709.48465828344</v>
       </c>
       <c r="AZ226" t="n">
-        <v>282.295880253193</v>
+        <v>282.537303714275</v>
       </c>
     </row>
     <row r="227">
@@ -36992,7 +36992,7 @@
         <v>279</v>
       </c>
       <c r="B227" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -37016,34 +37016,34 @@
         <v>0.0056310426470525</v>
       </c>
       <c r="J227" t="n">
-        <v>31470.0423678506</v>
+        <v>31532.8739323758</v>
       </c>
       <c r="K227" t="n">
-        <v>21480.4128000157</v>
+        <v>21417.6510788579</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M227" t="n">
-        <v>2015.66538114018</v>
+        <v>2026.77199455697</v>
       </c>
       <c r="N227" t="n">
-        <v>424.522897172307</v>
+        <v>404.4368788</v>
       </c>
       <c r="O227" t="n">
         <v>75.203</v>
       </c>
       <c r="P227" t="n">
-        <v>3369.56031809787</v>
+        <v>3372.78044478709</v>
       </c>
       <c r="Q227" t="n">
-        <v>4763.19252374503</v>
+        <v>5018.68661604681</v>
       </c>
       <c r="R227" t="n">
-        <v>2674.98941294424</v>
+        <v>2687.62095094217</v>
       </c>
       <c r="S227" t="n">
-        <v>408.442891766269</v>
+        <v>389.467852836203</v>
       </c>
       <c r="T227" t="n">
         <v>155.206844624839</v>
@@ -37052,7 +37052,7 @@
         <v>172.904788658593</v>
       </c>
       <c r="V227" t="n">
-        <v>2309.427190501</v>
+        <v>2420.73626997664</v>
       </c>
       <c r="W227" t="n">
         <v>245.190594913367</v>
@@ -37070,7 +37070,7 @@
         <v>35.7</v>
       </c>
       <c r="AB227" t="n">
-        <v>99.168</v>
+        <v>119.59</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -37082,31 +37082,31 @@
         <v>0</v>
       </c>
       <c r="AF227" t="n">
-        <v>2.71754</v>
+        <v>-8.28246</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>1955.44249641565</v>
+        <v>1969.6219827834</v>
       </c>
       <c r="AI227" t="n">
-        <v>325.264298549568</v>
+        <v>325.376600965333</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2809.10232560901</v>
+        <v>-2900.86463783576</v>
       </c>
       <c r="AK227" t="n">
-        <v>-1559.44733702866</v>
+        <v>-1564.75853441394</v>
       </c>
       <c r="AL227" t="n">
-        <v>-168.651840586777</v>
+        <v>-157.029164110608</v>
       </c>
       <c r="AM227" t="n">
-        <v>-67.7086969220617</v>
+        <v>-61.9655463049215</v>
       </c>
       <c r="AN227" t="n">
-        <v>2058.02513572545</v>
+        <v>2145.76688504374</v>
       </c>
       <c r="AO227" t="n">
         <v>215.94810271373</v>
@@ -37121,10 +37121,10 @@
         <v>0</v>
       </c>
       <c r="AS227" t="n">
-        <v>32.512</v>
+        <v>32.602</v>
       </c>
       <c r="AT227" t="n">
-        <v>44.52759</v>
+        <v>48.67858575</v>
       </c>
       <c r="AU227" t="n">
         <v>0.211344</v>
@@ -37133,16 +37133,16 @@
         <v>1.05376</v>
       </c>
       <c r="AW227" t="n">
-        <v>2.45433355</v>
+        <v>-5.02566645</v>
       </c>
       <c r="AX227" t="n">
-        <v>0.171675</v>
+        <v>0.1953</v>
       </c>
       <c r="AY227" t="n">
-        <v>1720.76799653542</v>
+        <v>1733.52905440971</v>
       </c>
       <c r="AZ227" t="n">
-        <v>286.592103594612</v>
+        <v>287.697588931475</v>
       </c>
     </row>
     <row r="228">
@@ -37150,7 +37150,7 @@
         <v>280</v>
       </c>
       <c r="B228" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -37174,34 +37174,34 @@
         <v>0.00558696597638098</v>
       </c>
       <c r="J228" t="n">
-        <v>31765.2157812239</v>
+        <v>31828.6366747101</v>
       </c>
       <c r="K228" t="n">
-        <v>21651.0005126672</v>
+        <v>21587.7403663369</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M228" t="n">
-        <v>2033.02179894024</v>
+        <v>2044.22404877794</v>
       </c>
       <c r="N228" t="n">
-        <v>428.448339862007</v>
+        <v>408.164405784728</v>
       </c>
       <c r="O228" t="n">
         <v>75.203</v>
       </c>
       <c r="P228" t="n">
-        <v>3399.64120333114</v>
+        <v>3402.89007687522</v>
       </c>
       <c r="Q228" t="n">
-        <v>4796.01431092621</v>
+        <v>5059.83103467339</v>
       </c>
       <c r="R228" t="n">
-        <v>2698.31224140776</v>
+        <v>2711.06551750846</v>
       </c>
       <c r="S228" t="n">
-        <v>405.919174395884</v>
+        <v>387.061379850081</v>
       </c>
       <c r="T228" t="n">
         <v>162.820344255939</v>
@@ -37210,7 +37210,7 @@
         <v>172.73187878435</v>
       </c>
       <c r="V228" t="n">
-        <v>2317.127190501</v>
+        <v>2438.09170309653</v>
       </c>
       <c r="W228" t="n">
         <v>248.77488506154</v>
@@ -37228,7 +37228,7 @@
         <v>35.7</v>
       </c>
       <c r="AB228" t="n">
-        <v>99.168</v>
+        <v>119.59</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -37240,31 +37240,31 @@
         <v>0</v>
       </c>
       <c r="AF228" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AG228" t="n">
         <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1984.88340620506</v>
+        <v>1997.46782381642</v>
       </c>
       <c r="AI228" t="n">
-        <v>330.213754227397</v>
+        <v>331.135171796343</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-2833.38924665272</v>
+        <v>-2941.97847492114</v>
       </c>
       <c r="AK228" t="n">
-        <v>-1575.62837412004</v>
+        <v>-1581.71969598878</v>
       </c>
       <c r="AL228" t="n">
-        <v>-167.119146399973</v>
+        <v>-154.867876772278</v>
       </c>
       <c r="AM228" t="n">
-        <v>-67.9364262148734</v>
+        <v>-62.1932755977332</v>
       </c>
       <c r="AN228" t="n">
-        <v>2067.34670358817</v>
+        <v>2163.47540836546</v>
       </c>
       <c r="AO228" t="n">
         <v>219.104914896297</v>
@@ -37279,10 +37279,10 @@
         <v>0</v>
       </c>
       <c r="AS228" t="n">
-        <v>32.508</v>
+        <v>32.558</v>
       </c>
       <c r="AT228" t="n">
-        <v>44.320248</v>
+        <v>49.16048625</v>
       </c>
       <c r="AU228" t="n">
         <v>-0.00499800000000003</v>
@@ -37291,16 +37291,16 @@
         <v>0.61906</v>
       </c>
       <c r="AW228" t="n">
-        <v>1.91853524</v>
+        <v>-6.55146476</v>
       </c>
       <c r="AX228" t="n">
-        <v>0.14805</v>
+        <v>0.171675</v>
       </c>
       <c r="AY228" t="n">
-        <v>1746.53552656238</v>
+        <v>1758.96242718879</v>
       </c>
       <c r="AZ228" t="n">
-        <v>291.083024035847</v>
+        <v>291.849437547487</v>
       </c>
     </row>
     <row r="229">
@@ -37308,7 +37308,7 @@
         <v>281</v>
       </c>
       <c r="B229" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -37332,34 +37332,34 @@
         <v>0.00554760795794795</v>
       </c>
       <c r="J229" t="n">
-        <v>32061.888044022</v>
+        <v>32125.9012589993</v>
       </c>
       <c r="K229" t="n">
-        <v>21844.2530242953</v>
+        <v>21780.4282305181</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M229" t="n">
-        <v>2043.3145583333</v>
+        <v>2054.57352279269</v>
       </c>
       <c r="N229" t="n">
-        <v>430.402608127864</v>
+        <v>409.918808201709</v>
       </c>
       <c r="O229" t="n">
         <v>75.203</v>
       </c>
       <c r="P229" t="n">
-        <v>3428.99713798472</v>
+        <v>3432.27406558326</v>
       </c>
       <c r="Q229" t="n">
-        <v>4829.21435475184</v>
+        <v>5101.36887514672</v>
       </c>
       <c r="R229" t="n">
-        <v>2723.57333674919</v>
+        <v>2736.45208782637</v>
       </c>
       <c r="S229" t="n">
-        <v>403.411050758414</v>
+        <v>384.669776158537</v>
       </c>
       <c r="T229" t="n">
         <v>160.445027356869</v>
@@ -37368,7 +37368,7 @@
         <v>172.940387750349</v>
       </c>
       <c r="V229" t="n">
-        <v>2316.672190501</v>
+        <v>2447.30891338201</v>
       </c>
       <c r="W229" t="n">
         <v>252.41157173769</v>
@@ -37386,7 +37386,7 @@
         <v>35.7</v>
       </c>
       <c r="AB229" t="n">
-        <v>99.168</v>
+        <v>119.59</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -37398,31 +37398,31 @@
         <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>2002.08812793393</v>
+        <v>2014.7548505226</v>
       </c>
       <c r="AI229" t="n">
-        <v>329.321583987845</v>
+        <v>330.366464938642</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-2855.12941779824</v>
+        <v>-2981.04754297593</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1590.76980975328</v>
+        <v>-1597.64868947141</v>
       </c>
       <c r="AL229" t="n">
-        <v>-165.07284809192</v>
+        <v>-152.196869310896</v>
       </c>
       <c r="AM229" t="n">
-        <v>-68.1377724732184</v>
+        <v>-62.3946218560782</v>
       </c>
       <c r="AN229" t="n">
-        <v>2080.5033964509</v>
+        <v>2185.03404382704</v>
       </c>
       <c r="AO229" t="n">
         <v>222.307874570001</v>
@@ -37437,10 +37437,10 @@
         <v>0</v>
       </c>
       <c r="AS229" t="n">
-        <v>32.491</v>
+        <v>32.541</v>
       </c>
       <c r="AT229" t="n">
-        <v>44.248968</v>
+        <v>49.77844875</v>
       </c>
       <c r="AU229" t="n">
         <v>-0.028203</v>
@@ -37449,16 +37449,16 @@
         <v>0.37618</v>
       </c>
       <c r="AW229" t="n">
-        <v>1.46096398</v>
+        <v>-7.55903602</v>
       </c>
       <c r="AX229" t="n">
-        <v>0.124425</v>
+        <v>0.14805</v>
       </c>
       <c r="AY229" t="n">
-        <v>1769.985880427</v>
+        <v>1782.0810601233</v>
       </c>
       <c r="AZ229" t="n">
-        <v>294.173343209048</v>
+        <v>294.804455387384</v>
       </c>
     </row>
     <row r="230">
@@ -37466,7 +37466,7 @@
         <v>282</v>
       </c>
       <c r="B230" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -37490,34 +37490,34 @@
         <v>0.00550459474437348</v>
       </c>
       <c r="J230" t="n">
-        <v>32366.1544772386</v>
+        <v>32430.7751758605</v>
       </c>
       <c r="K230" t="n">
-        <v>22049.8408026231</v>
+        <v>21985.4153200725</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="M230" t="n">
-        <v>2053.00186129147</v>
+        <v>2064.31420421835</v>
       </c>
       <c r="N230" t="n">
-        <v>433.385986</v>
+        <v>412.700350865505</v>
       </c>
       <c r="O230" t="n">
         <v>75.203</v>
       </c>
       <c r="P230" t="n">
-        <v>3457.71231495272</v>
+        <v>3461.01668426442</v>
       </c>
       <c r="Q230" t="n">
-        <v>4959.97196525287</v>
+        <v>5247.53110881393</v>
       </c>
       <c r="R230" t="n">
-        <v>2750.26808656332</v>
+        <v>2763.27850728241</v>
       </c>
       <c r="S230" t="n">
-        <v>412.618424502142</v>
+        <v>392.292949886067</v>
       </c>
       <c r="T230" t="n">
         <v>146.435353395161</v>
@@ -37526,7 +37526,7 @@
         <v>172.609824755473</v>
       </c>
       <c r="V230" t="n">
-        <v>2365.24405938352</v>
+        <v>2504.06277557692</v>
       </c>
       <c r="W230" t="n">
         <v>256.101420894358</v>
@@ -37544,7 +37544,7 @@
         <v>36.7</v>
       </c>
       <c r="AB230" t="n">
-        <v>99.168</v>
+        <v>119.59</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -37556,31 +37556,31 @@
         <v>0</v>
       </c>
       <c r="AF230" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>2032.18374581113</v>
+        <v>2044.9908675864</v>
       </c>
       <c r="AI230" t="n">
-        <v>334.235231621928</v>
+        <v>335.348548293239</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-2884.12319497301</v>
+        <v>-3028.7194139532</v>
       </c>
       <c r="AK230" t="n">
-        <v>-1605.87324565642</v>
+        <v>-1613.54817929479</v>
       </c>
       <c r="AL230" t="n">
-        <v>-163.496795575325</v>
+        <v>-149.943300973764</v>
       </c>
       <c r="AM230" t="n">
-        <v>-68.2114332984008</v>
+        <v>-62.4682826812606</v>
       </c>
       <c r="AN230" t="n">
-        <v>2094.40589194947</v>
+        <v>2207.29492395722</v>
       </c>
       <c r="AO230" t="n">
         <v>225.557656336565</v>
@@ -37595,10 +37595,10 @@
         <v>0</v>
       </c>
       <c r="AS230" t="n">
-        <v>32.687</v>
+        <v>32.727</v>
       </c>
       <c r="AT230" t="n">
-        <v>44.229213</v>
+        <v>50.44793625</v>
       </c>
       <c r="AU230" t="n">
         <v>-0.051408</v>
@@ -37607,16 +37607,16 @@
         <v>0.23798</v>
       </c>
       <c r="AW230" t="n">
-        <v>1.0295209</v>
+        <v>-8.5404791</v>
       </c>
       <c r="AX230" t="n">
-        <v>0.1008</v>
+        <v>0.124425</v>
       </c>
       <c r="AY230" t="n">
-        <v>1794.2844996823</v>
+        <v>1806.03799305949</v>
       </c>
       <c r="AZ230" t="n">
-        <v>296.782845387016</v>
+        <v>297.50102684855</v>
       </c>
     </row>
     <row r="231">
@@ -37624,7 +37624,7 @@
         <v>283</v>
       </c>
       <c r="B231" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -37648,46 +37648,46 @@
         <v>0.00545389484594594</v>
       </c>
       <c r="J231" t="n">
-        <v>32662.3271235618</v>
+        <v>32727.5391461647</v>
       </c>
       <c r="K231" t="n">
-        <v>22233.26521558</v>
+        <v>22168.3038014359</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>2075.57686711676</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>415.5093012</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>75.203</v>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>3490.55682467248</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>5279.96277282185</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>2788.05586111262</v>
       </c>
       <c r="S231" t="n">
-        <v>0</v>
+        <v>389.869020979811</v>
       </c>
       <c r="T231" t="n">
-        <v>0</v>
+        <v>123.274912601363</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>171.974126688402</v>
       </c>
       <c r="V231" t="n">
-        <v>0</v>
+        <v>2521.46879227051</v>
       </c>
       <c r="W231" t="n">
-        <v>0</v>
+        <v>259.845209681073</v>
       </c>
       <c r="X231" t="n">
         <v>0</v>
@@ -37699,10 +37699,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="AB231" t="n">
-        <v>0</v>
+        <v>119.59</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -37714,34 +37714,34 @@
         <v>0</v>
       </c>
       <c r="AF231" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>0</v>
+        <v>2076.09258663117</v>
       </c>
       <c r="AI231" t="n">
-        <v>0</v>
+        <v>339.993837870728</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-2311.78124999068</v>
+        <v>-3063.96081418302</v>
       </c>
       <c r="AK231" t="n">
-        <v>-1288.1947172475</v>
+        <v>-1628.84575735872</v>
       </c>
       <c r="AL231" t="n">
-        <v>-147.050128908658</v>
+        <v>-146.492268339758</v>
       </c>
       <c r="AM231" t="n">
-        <v>-62.7447666317341</v>
+        <v>-62.7340869042074</v>
       </c>
       <c r="AN231" t="n">
-        <v>1574.78477408674</v>
+        <v>2229.95974147334</v>
       </c>
       <c r="AO231" t="n">
-        <v>170.389772481057</v>
+        <v>228.854944659299</v>
       </c>
       <c r="AP231" t="n">
         <v>0</v>
@@ -37753,10 +37753,10 @@
         <v>0</v>
       </c>
       <c r="AS231" t="n">
-        <v>25.517</v>
+        <v>33.057</v>
       </c>
       <c r="AT231" t="n">
-        <v>39.40990875</v>
+        <v>51.09492375</v>
       </c>
       <c r="AU231" t="n">
         <v>-0.074613</v>
@@ -37765,16 +37765,16 @@
         <v>0.11938</v>
       </c>
       <c r="AW231" t="n">
-        <v>0.62405284</v>
+        <v>-9.38594716</v>
       </c>
       <c r="AX231" t="n">
-        <v>0.0819</v>
+        <v>0.1008</v>
       </c>
       <c r="AY231" t="n">
-        <v>1354.30993798878</v>
+        <v>1829.99387892524</v>
       </c>
       <c r="AZ231" t="n">
-        <v>223.598378213363</v>
+        <v>300.789905152264</v>
       </c>
     </row>
     <row r="232">
@@ -37782,7 +37782,7 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -37806,10 +37806,10 @@
         <v>0.00542022049047874</v>
       </c>
       <c r="J232" t="n">
-        <v>32962.0970085043</v>
+        <v>33027.907537161</v>
       </c>
       <c r="K232" t="n">
-        <v>22417.1910621425</v>
+        <v>22351.6922513104</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37884,22 +37884,22 @@
         <v>0</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-1730.17944410719</v>
+        <v>-2456.05225949952</v>
       </c>
       <c r="AK232" t="n">
-        <v>-967.287936372096</v>
+        <v>-1306.42397082385</v>
       </c>
       <c r="AL232" t="n">
-        <v>-130.613462241992</v>
+        <v>-130.055601673092</v>
       </c>
       <c r="AM232" t="n">
-        <v>-57.3247666317341</v>
+        <v>-57.3140869042074</v>
       </c>
       <c r="AN232" t="n">
-        <v>1053.43115622402</v>
+        <v>1681.38910827663</v>
       </c>
       <c r="AO232" t="n">
-        <v>114.415423342211</v>
+        <v>172.880595520452</v>
       </c>
       <c r="AP232" t="n">
         <v>0</v>
@@ -37911,10 +37911,10 @@
         <v>0</v>
       </c>
       <c r="AS232" t="n">
-        <v>19.438</v>
+        <v>25.847</v>
       </c>
       <c r="AT232" t="n">
-        <v>35.2689885</v>
+        <v>45.8251245</v>
       </c>
       <c r="AU232" t="n">
         <v>-0.097818</v>
@@ -37923,16 +37923,16 @@
         <v>0.0196</v>
       </c>
       <c r="AW232" t="n">
-        <v>0.3804556</v>
+        <v>-7.4295444</v>
       </c>
       <c r="AX232" t="n">
-        <v>0.063</v>
+        <v>0.0819</v>
       </c>
       <c r="AY232" t="n">
-        <v>907.711171592638</v>
+        <v>1380.56361856654</v>
       </c>
       <c r="AZ232" t="n">
-        <v>149.300283512199</v>
+        <v>226.284491498087</v>
       </c>
     </row>
     <row r="233">
@@ -37940,7 +37940,7 @@
         <v>285</v>
       </c>
       <c r="B233" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -37964,10 +37964,10 @@
         <v>0.00537879404345354</v>
       </c>
       <c r="J233" t="n">
-        <v>33272.5586860097</v>
+        <v>33338.989067436</v>
       </c>
       <c r="K233" t="n">
-        <v>22614.3547558949</v>
+        <v>22548.2798698782</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -38042,22 +38042,22 @@
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-1444.748385548</v>
+        <v>-1841.1187115256</v>
       </c>
       <c r="AK233" t="n">
-        <v>-809.795016537425</v>
+        <v>-980.905076006506</v>
       </c>
       <c r="AL233" t="n">
-        <v>-113.543462241992</v>
+        <v>-112.985601673092</v>
       </c>
       <c r="AM233" t="n">
-        <v>-51.8514332984008</v>
+        <v>-51.840753570874</v>
       </c>
       <c r="AN233" t="n">
-        <v>532.179913361293</v>
+        <v>1130.74460276567</v>
       </c>
       <c r="AO233" t="n">
-        <v>57.6228197012306</v>
+        <v>116.087991879472</v>
       </c>
       <c r="AP233" t="n">
         <v>0</v>
@@ -38069,10 +38069,10 @@
         <v>0</v>
       </c>
       <c r="AS233" t="n">
-        <v>13.716</v>
+        <v>19.748</v>
       </c>
       <c r="AT233" t="n">
-        <v>31.342608</v>
+        <v>41.3539695</v>
       </c>
       <c r="AU233" t="n">
         <v>-0.082501</v>
@@ -38081,16 +38081,16 @@
         <v>0</v>
       </c>
       <c r="AW233" t="n">
-        <v>0.2445786</v>
+        <v>-5.6954214</v>
       </c>
       <c r="AX233" t="n">
-        <v>0.0441</v>
+        <v>0.063</v>
       </c>
       <c r="AY233" t="n">
-        <v>457.241342807504</v>
+        <v>927.243777198955</v>
       </c>
       <c r="AZ233" t="n">
-        <v>75.2029271149338</v>
+        <v>151.952036886893</v>
       </c>
     </row>
     <row r="234">
@@ -38098,7 +38098,7 @@
         <v>286</v>
       </c>
       <c r="B234" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -38122,10 +38122,10 @@
         <v>0.00534192357811758</v>
       </c>
       <c r="J234" t="n">
-        <v>33585.6183691846</v>
+        <v>33652.6737904331</v>
       </c>
       <c r="K234" t="n">
-        <v>22821.5471217609</v>
+        <v>22754.8668586682</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -38200,22 +38200,22 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-1160.90358928056</v>
+        <v>-1542.44282445016</v>
       </c>
       <c r="AK234" t="n">
-        <v>-650.82858465987</v>
+        <v>-821.188375480322</v>
       </c>
       <c r="AL234" t="n">
-        <v>-96.216795575325</v>
+        <v>-95.6589350064249</v>
       </c>
       <c r="AM234" t="n">
-        <v>-46.0280999650675</v>
+        <v>-46.0174202375407</v>
       </c>
       <c r="AN234" t="n">
-        <v>0</v>
+        <v>567.330478260866</v>
       </c>
       <c r="AO234" t="n">
-        <v>0</v>
+        <v>58.4651721782414</v>
       </c>
       <c r="AP234" t="n">
         <v>0</v>
@@ -38227,10 +38227,10 @@
         <v>0</v>
       </c>
       <c r="AS234" t="n">
-        <v>8.301</v>
+        <v>13.956</v>
       </c>
       <c r="AT234" t="n">
-        <v>27.488268</v>
+        <v>37.0008045</v>
       </c>
       <c r="AU234" t="n">
         <v>-0.067184</v>
@@ -38239,16 +38239,16 @@
         <v>0</v>
       </c>
       <c r="AW234" t="n">
-        <v>0.1087016</v>
+        <v>-4.0712984</v>
       </c>
       <c r="AX234" t="n">
-        <v>0.0252</v>
+        <v>0.0441</v>
       </c>
       <c r="AY234" t="n">
-        <v>0</v>
+        <v>467.120831992014</v>
       </c>
       <c r="AZ234" t="n">
-        <v>0</v>
+        <v>76.4986135209138</v>
       </c>
     </row>
     <row r="235">
@@ -38256,7 +38256,7 @@
         <v>287</v>
       </c>
       <c r="B235" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -38280,10 +38280,10 @@
         <v>0.00532158987529296</v>
       </c>
       <c r="J235" t="n">
-        <v>33891.083881941</v>
+        <v>33958.7491808582</v>
       </c>
       <c r="K235" t="n">
-        <v>23026.3326063196</v>
+        <v>22959.0539986048</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -38358,16 +38358,16 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-875.112037855855</v>
+        <v>-1241.32162748735</v>
       </c>
       <c r="AK235" t="n">
-        <v>-490.329219883216</v>
+        <v>-659.931118423792</v>
       </c>
       <c r="AL235" t="n">
-        <v>-78.3197384448368</v>
+        <v>-95.6589350064249</v>
       </c>
       <c r="AM235" t="n">
-        <v>-40.2849493479273</v>
+        <v>-46.0174202375407</v>
       </c>
       <c r="AN235" t="n">
         <v>0</v>
@@ -38385,10 +38385,10 @@
         <v>0</v>
       </c>
       <c r="AS235" t="n">
-        <v>5.048</v>
+        <v>8.441</v>
       </c>
       <c r="AT235" t="n">
-        <v>24.229962</v>
+        <v>32.715117</v>
       </c>
       <c r="AU235" t="n">
         <v>-0.051867</v>
@@ -38397,10 +38397,10 @@
         <v>0</v>
       </c>
       <c r="AW235" t="n">
-        <v>0</v>
+        <v>-2.53</v>
       </c>
       <c r="AX235" t="n">
-        <v>0.0189</v>
+        <v>0.0252</v>
       </c>
       <c r="AY235" t="n">
         <v>0</v>
@@ -38414,7 +38414,7 @@
         <v>288</v>
       </c>
       <c r="B236" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -38438,10 +38438,10 @@
         <v>0.00528941636235492</v>
       </c>
       <c r="J236" t="n">
-        <v>34205.3426446557</v>
+        <v>34273.6353774192</v>
       </c>
       <c r="K236" t="n">
-        <v>23242.1496302033</v>
+        <v>23174.2404457858</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -38516,16 +38516,16 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-587.351179200283</v>
+        <v>-937.731765406951</v>
       </c>
       <c r="AK236" t="n">
-        <v>-328.43048539875</v>
+        <v>-497.267187373284</v>
       </c>
       <c r="AL236" t="n">
-        <v>-73.1668470418124</v>
+        <v>-90.9858681442722</v>
       </c>
       <c r="AM236" t="n">
-        <v>-34.5368826657351</v>
+        <v>-40.2693535553485</v>
       </c>
       <c r="AN236" t="n">
         <v>0</v>
@@ -38543,10 +38543,10 @@
         <v>0</v>
       </c>
       <c r="AS236" t="n">
-        <v>3.263</v>
+        <v>5.148</v>
       </c>
       <c r="AT236" t="n">
-        <v>20.986056</v>
+        <v>28.9657665</v>
       </c>
       <c r="AU236" t="n">
         <v>-0.03655</v>
@@ -38555,10 +38555,10 @@
         <v>0</v>
       </c>
       <c r="AW236" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="AX236" t="n">
-        <v>0.0126</v>
+        <v>0.0189</v>
       </c>
       <c r="AY236" t="n">
         <v>0</v>
@@ -38572,7 +38572,7 @@
         <v>289</v>
       </c>
       <c r="B237" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -38596,10 +38596,10 @@
         <v>0.00524963654830413</v>
       </c>
       <c r="J237" t="n">
-        <v>34526.895807904</v>
+        <v>34595.8305381611</v>
       </c>
       <c r="K237" t="n">
-        <v>23461.8778362112</v>
+        <v>23393.3266473535</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -38674,16 +38674,16 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-297.598317915172</v>
+        <v>-631.649632898147</v>
       </c>
       <c r="AK237" t="n">
-        <v>-165.016085193799</v>
+        <v>-333.080062103702</v>
       </c>
       <c r="AL237" t="n">
-        <v>-68.0457947081014</v>
+        <v>-77.8416755758108</v>
       </c>
       <c r="AM237" t="n">
-        <v>-28.7916978147803</v>
+        <v>-34.5241687043937</v>
       </c>
       <c r="AN237" t="n">
         <v>0</v>
@@ -38701,10 +38701,10 @@
         <v>0</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.468</v>
+        <v>3.353</v>
       </c>
       <c r="AT237" t="n">
-        <v>17.651448</v>
+        <v>25.125714</v>
       </c>
       <c r="AU237" t="n">
         <v>0</v>
@@ -38713,10 +38713,10 @@
         <v>0</v>
       </c>
       <c r="AW237" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="AX237" t="n">
-        <v>0.0063</v>
+        <v>0.0126</v>
       </c>
       <c r="AY237" t="n">
         <v>0</v>
@@ -38730,7 +38730,7 @@
         <v>290</v>
       </c>
       <c r="B238" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -38754,10 +38754,10 @@
         <v>0.00521033508596069</v>
       </c>
       <c r="J238" t="n">
-        <v>34853.9447523762</v>
+        <v>34923.532452738</v>
       </c>
       <c r="K238" t="n">
-        <v>23691.5344276115</v>
+        <v>23622.3122254411</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -38832,16 +38832,16 @@
         <v>0</v>
       </c>
       <c r="AJ238" t="n">
-        <v>0</v>
+        <v>-316.797766369311</v>
       </c>
       <c r="AK238" t="n">
-        <v>0</v>
+        <v>-167.283351666757</v>
       </c>
       <c r="AL238" t="n">
-        <v>-54.3463847140902</v>
+        <v>-64.7786993236899</v>
       </c>
       <c r="AM238" t="n">
-        <v>-23.0395626649588</v>
+        <v>-28.7720335545722</v>
       </c>
       <c r="AN238" t="n">
         <v>0</v>
@@ -38859,10 +38859,10 @@
         <v>0</v>
       </c>
       <c r="AS238" t="n">
-        <v>0</v>
+        <v>1.508</v>
       </c>
       <c r="AT238" t="n">
-        <v>14.26014</v>
+        <v>21.2289615</v>
       </c>
       <c r="AU238" t="n">
         <v>0</v>
@@ -38871,10 +38871,10 @@
         <v>0</v>
       </c>
       <c r="AW238" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="AX238" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="AY238" t="n">
         <v>0</v>
@@ -38888,7 +38888,7 @@
         <v>291</v>
       </c>
       <c r="B239" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -38912,10 +38912,10 @@
         <v>0.00516756143130825</v>
       </c>
       <c r="J239" t="n">
-        <v>35184.0913189928</v>
+        <v>35254.3381740218</v>
       </c>
       <c r="K239" t="n">
-        <v>23926.7067886743</v>
+        <v>23856.7974571509</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -38996,10 +38996,10 @@
         <v>0</v>
       </c>
       <c r="AL239" t="n">
-        <v>-40.7316216552146</v>
+        <v>-51.7964375624831</v>
       </c>
       <c r="AM239" t="n">
-        <v>-17.2760697096724</v>
+        <v>-23.0085405992858</v>
       </c>
       <c r="AN239" t="n">
         <v>0</v>
@@ -39020,7 +39020,7 @@
         <v>0</v>
       </c>
       <c r="AT239" t="n">
-        <v>11.602305</v>
+        <v>17.220609</v>
       </c>
       <c r="AU239" t="n">
         <v>0</v>
@@ -39046,7 +39046,7 @@
         <v>292</v>
       </c>
       <c r="B240" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -39070,10 +39070,10 @@
         <v>0.00510570215168871</v>
       </c>
       <c r="J240" t="n">
-        <v>35516.1364282141</v>
+        <v>35587.0462284486</v>
       </c>
       <c r="K240" t="n">
-        <v>24158.9708348241</v>
+        <v>24088.3828714962</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -39154,10 +39154,10 @@
         <v>0</v>
       </c>
       <c r="AL240" t="n">
-        <v>-27.2009825086852</v>
+        <v>-38.8943915674805</v>
       </c>
       <c r="AM240" t="n">
-        <v>-11.5183404168607</v>
+        <v>-17.2508113064741</v>
       </c>
       <c r="AN240" t="n">
         <v>0</v>
@@ -39178,7 +39178,7 @@
         <v>0</v>
       </c>
       <c r="AT240" t="n">
-        <v>8.94447</v>
+        <v>14.01138</v>
       </c>
       <c r="AU240" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>293</v>
       </c>
       <c r="B241" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -39228,10 +39228,10 @@
         <v>0.00504465278509314</v>
       </c>
       <c r="J241" t="n">
-        <v>35850.6796198099</v>
+        <v>35922.2573528004</v>
       </c>
       <c r="K241" t="n">
-        <v>24394.0429091658</v>
+        <v>24322.7681095038</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -39312,10 +39312,10 @@
         <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>-13.7539474834047</v>
+        <v>-26.0720656955292</v>
       </c>
       <c r="AM241" t="n">
-        <v>-5.75366082518242</v>
+        <v>-11.4861317147958</v>
       </c>
       <c r="AN241" t="n">
         <v>0</v>
@@ -39336,7 +39336,7 @@
         <v>0</v>
       </c>
       <c r="AT241" t="n">
-        <v>6.247584</v>
+        <v>10.7631</v>
       </c>
       <c r="AU241" t="n">
         <v>0</v>
@@ -39362,7 +39362,7 @@
         <v>294</v>
       </c>
       <c r="B242" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -39386,10 +39386,10 @@
         <v>0.00499215850685553</v>
       </c>
       <c r="J242" t="n">
-        <v>36191.9176721694</v>
+        <v>36264.1767045511</v>
       </c>
       <c r="K242" t="n">
-        <v>24637.8399282462</v>
+        <v>24565.8527996047</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -39470,10 +39470,10 @@
         <v>0</v>
       </c>
       <c r="AL242" t="n">
-        <v>0</v>
+        <v>-12.9956340326603</v>
       </c>
       <c r="AM242" t="n">
-        <v>0</v>
+        <v>-5.73247088961341</v>
       </c>
       <c r="AN242" t="n">
         <v>0</v>
@@ -39494,7 +39494,7 @@
         <v>0</v>
       </c>
       <c r="AT242" t="n">
-        <v>3.570048</v>
+        <v>7.53417</v>
       </c>
       <c r="AU242" t="n">
         <v>0</v>
@@ -39520,7 +39520,7 @@
         <v>295</v>
       </c>
       <c r="B243" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -39544,10 +39544,10 @@
         <v>0.00493645950017374</v>
       </c>
       <c r="J243" t="n">
-        <v>36539.7506619977</v>
+        <v>36612.7041609037</v>
       </c>
       <c r="K243" t="n">
-        <v>24895.6770882856</v>
+        <v>24822.9366080166</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -39652,7 +39652,7 @@
         <v>0</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.677536</v>
+        <v>4.30524</v>
       </c>
       <c r="AU243" t="n">
         <v>0</v>
@@ -39678,7 +39678,7 @@
         <v>296</v>
       </c>
       <c r="B244" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -39702,10 +39702,10 @@
         <v>0.00488530487992378</v>
       </c>
       <c r="J244" t="n">
-        <v>36880.9887143572</v>
+        <v>36954.6235126544</v>
       </c>
       <c r="K244" t="n">
-        <v>25151.1073670177</v>
+        <v>25077.6205675751</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -39810,7 +39810,7 @@
         <v>0</v>
       </c>
       <c r="AT244" t="n">
-        <v>1.785024</v>
+        <v>3.22893</v>
       </c>
       <c r="AU244" t="n">
         <v>0</v>
@@ -39836,7 +39836,7 @@
         <v>297</v>
       </c>
       <c r="B245" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -39860,10 +39860,10 @@
         <v>0.00484625476688616</v>
       </c>
       <c r="J245" t="n">
-        <v>37229.9208604302</v>
+        <v>37304.252319774</v>
       </c>
       <c r="K245" t="n">
-        <v>25413.3571427871</v>
+        <v>25339.1040988848</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -39968,7 +39968,7 @@
         <v>0</v>
       </c>
       <c r="AT245" t="n">
-        <v>0.892512</v>
+        <v>2.15262</v>
       </c>
       <c r="AU245" t="n">
         <v>0</v>
@@ -39994,7 +39994,7 @@
         <v>298</v>
       </c>
       <c r="B246" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -40018,10 +40018,10 @@
         <v>0.0048076557063792</v>
       </c>
       <c r="J246" t="n">
-        <v>37582.6500917125</v>
+        <v>37657.6857931795</v>
       </c>
       <c r="K246" t="n">
-        <v>25676.4092123256</v>
+        <v>25601.3875798122</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -40126,7 +40126,7 @@
         <v>0</v>
       </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>1.07631</v>
       </c>
       <c r="AU246" t="n">
         <v>0</v>
@@ -40152,7 +40152,7 @@
         <v>299</v>
       </c>
       <c r="B247" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -40176,10 +40176,10 @@
         <v>0.00478086441968562</v>
       </c>
       <c r="J247" t="n">
-        <v>37939.476178089</v>
+        <v>38015.224301262</v>
       </c>
       <c r="K247" t="n">
-        <v>25946.080205459</v>
+        <v>25870.2706450863</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -40310,7 +40310,7 @@
         <v>300</v>
       </c>
       <c r="B248" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -40334,10 +40334,10 @@
         <v>0.00473926501804089</v>
       </c>
       <c r="J248" t="n">
-        <v>38300.4990428548</v>
+        <v>38376.9679668184</v>
       </c>
       <c r="K248" t="n">
-        <v>26215.6509118712</v>
+        <v>26139.0537166581</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -40468,7 +40468,7 @@
         <v>301</v>
       </c>
       <c r="B249" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -40492,10 +40492,10 @@
         <v>0.00471315781573667</v>
       </c>
       <c r="J249" t="n">
-        <v>38665.7186860097</v>
+        <v>38742.9167898488</v>
       </c>
       <c r="K249" t="n">
-        <v>26487.2273527062</v>
+        <v>26409.8366622744</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -40626,7 +40626,7 @@
         <v>302</v>
       </c>
       <c r="B250" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -40650,10 +40650,10 @@
         <v>0.00467984343253258</v>
       </c>
       <c r="J250" t="n">
-        <v>39034.5355677839</v>
+        <v>39112.4700335711</v>
       </c>
       <c r="K250" t="n">
-        <v>26761.4112482907</v>
+        <v>26683.2194441484</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -40784,7 +40784,7 @@
         <v>303</v>
       </c>
       <c r="B251" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -40808,10 +40808,10 @@
         <v>0.0046431744591946</v>
       </c>
       <c r="J251" t="n">
-        <v>39406.6499182925</v>
+        <v>39485.3273295944</v>
       </c>
       <c r="K251" t="n">
-        <v>27038.9046056727</v>
+        <v>26959.9020181957</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -40942,7 +40942,7 @@
         <v>304</v>
       </c>
       <c r="B252" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -40966,10 +40966,10 @@
         <v>0.00460321336856051</v>
       </c>
       <c r="J252" t="n">
-        <v>39782.4614307154</v>
+        <v>39861.8891691067</v>
       </c>
       <c r="K252" t="n">
-        <v>27319.5068514098</v>
+        <v>27239.6843970119</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -41100,7 +41100,7 @@
         <v>305</v>
       </c>
       <c r="B253" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -41124,10 +41124,10 @@
         <v>0.00457107075767049</v>
       </c>
       <c r="J253" t="n">
-        <v>40161.6703351676</v>
+        <v>40241.8551837169</v>
       </c>
       <c r="K253" t="n">
-        <v>27603.3182722233</v>
+        <v>27522.6665742992</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -41258,7 +41258,7 @@
         <v>306</v>
       </c>
       <c r="B254" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -41282,10 +41282,10 @@
         <v>0.00449893851450689</v>
       </c>
       <c r="J254" t="n">
-        <v>40541.8784725696</v>
+        <v>40622.822426297</v>
       </c>
       <c r="K254" t="n">
-        <v>27889.436287623</v>
+        <v>27807.9486067377</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -41416,7 +41416,7 @@
         <v>307</v>
       </c>
       <c r="B255" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -41440,10 +41440,10 @@
         <v>0.00453719183232471</v>
       </c>
       <c r="J255" t="n">
-        <v>40927.2826213107</v>
+        <v>41008.9960543212</v>
       </c>
       <c r="K255" t="n">
-        <v>28180.8694992428</v>
+        <v>28098.5303053938</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -41574,7 +41574,7 @@
         <v>308</v>
       </c>
       <c r="B256" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -41598,10 +41598,10 @@
         <v>0.00452033241158278</v>
       </c>
       <c r="J256" t="n">
-        <v>41315.4846223112</v>
+        <v>41397.9731206613</v>
       </c>
       <c r="K256" t="n">
-        <v>28475.7124593812</v>
+        <v>28392.5117899255</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -41732,7 +41732,7 @@
         <v>309</v>
       </c>
       <c r="B257" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -41756,10 +41756,10 @@
         <v>0.00449275624446099</v>
       </c>
       <c r="J257" t="n">
-        <v>41705.9848590962</v>
+        <v>41789.2530113323</v>
       </c>
       <c r="K257" t="n">
-        <v>28772.6614406634</v>
+        <v>28688.5931422038</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -41890,7 +41890,7 @@
         <v>310</v>
       </c>
       <c r="B258" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -41914,10 +41914,10 @@
         <v>0.00446545931210318</v>
       </c>
       <c r="J258" t="n">
-        <v>42098.8832549608</v>
+        <v>42182.9358491313</v>
       </c>
       <c r="K258" t="n">
-        <v>29071.5158696473</v>
+        <v>28986.5743748244</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -42048,7 +42048,7 @@
         <v>311</v>
       </c>
       <c r="B259" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -42072,10 +42072,10 @@
         <v>0.00443843729721394</v>
       </c>
       <c r="J259" t="n">
-        <v>42494.3796564949</v>
+        <v>42579.2218796523</v>
       </c>
       <c r="K259" t="n">
-        <v>29372.9777533806</v>
+        <v>29287.1554437027</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -42206,7 +42206,7 @@
         <v>312</v>
       </c>
       <c r="B260" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -42230,10 +42230,10 @@
         <v>0.00440811664554808</v>
       </c>
       <c r="J260" t="n">
-        <v>42892.5739869935</v>
+        <v>42978.2112256923</v>
       </c>
       <c r="K260" t="n">
-        <v>29678.150245796</v>
+        <v>29591.4362795632</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
